--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0453</v>
+        <v>-0.024</v>
       </c>
       <c r="E2">
-        <v>0.07469999999999999</v>
+        <v>0.02365</v>
       </c>
       <c r="F2">
-        <v>0.0476</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="G2">
-        <v>0.07949053708439897</v>
+        <v>0.1715256506870022</v>
       </c>
       <c r="H2">
-        <v>0.07949053708439897</v>
+        <v>0.1715256506870022</v>
       </c>
       <c r="I2">
-        <v>0.1145759590792839</v>
+        <v>0.1138224810534279</v>
       </c>
       <c r="J2">
-        <v>0.09313142872417118</v>
+        <v>0.0929554041707483</v>
       </c>
       <c r="K2">
-        <v>6163.6</v>
+        <v>6434.6</v>
       </c>
       <c r="L2">
-        <v>0.06305473145780051</v>
+        <v>0.09489286836132613</v>
       </c>
       <c r="M2">
-        <v>4112.578</v>
+        <v>4686.5</v>
       </c>
       <c r="N2">
-        <v>0.05132055740867609</v>
+        <v>0.05488309017620207</v>
       </c>
       <c r="O2">
-        <v>0.6672363553767278</v>
+        <v>0.7283281012028719</v>
       </c>
       <c r="P2">
-        <v>3852.848</v>
+        <v>4141.8</v>
       </c>
       <c r="Q2">
-        <v>0.04807940590328083</v>
+        <v>0.0485041679060693</v>
       </c>
       <c r="R2">
-        <v>0.6250970212213641</v>
+        <v>0.6436763745998197</v>
       </c>
       <c r="S2">
-        <v>259.73</v>
+        <v>544.7</v>
       </c>
       <c r="T2">
-        <v>0.06315503316897578</v>
+        <v>0.1162274618585298</v>
       </c>
       <c r="U2">
-        <v>13888.3</v>
+        <v>11836.8</v>
       </c>
       <c r="V2">
-        <v>0.1733110709289687</v>
+        <v>0.1386194733378147</v>
       </c>
       <c r="W2">
-        <v>0.09317421619273814</v>
+        <v>0.07725561658346544</v>
       </c>
       <c r="X2">
-        <v>0.051449230280752</v>
+        <v>0.08431794422051747</v>
       </c>
       <c r="Y2">
-        <v>0.04172498591198613</v>
+        <v>-0.007062327637052029</v>
       </c>
       <c r="Z2">
-        <v>1.988037202226602</v>
+        <v>1.172024184014214</v>
       </c>
       <c r="AA2">
-        <v>0.1346842929131344</v>
+        <v>0.06785235267976047</v>
       </c>
       <c r="AB2">
-        <v>0.04392948576571322</v>
+        <v>0.07345148270520499</v>
       </c>
       <c r="AC2">
-        <v>0.09075211867209639</v>
+        <v>-0.006196167120356567</v>
       </c>
       <c r="AD2">
-        <v>22307.7</v>
+        <v>21878.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>22307.7</v>
+        <v>21878.9</v>
       </c>
       <c r="AG2">
-        <v>8419.400000000001</v>
+        <v>10042.1</v>
       </c>
       <c r="AH2">
-        <v>0.2177576169335473</v>
+        <v>0.2039619836020491</v>
       </c>
       <c r="AI2">
-        <v>0.2854837471205529</v>
+        <v>0.3417664967641458</v>
       </c>
       <c r="AJ2">
-        <v>0.09507591370286096</v>
+        <v>0.1052270343393826</v>
       </c>
       <c r="AK2">
-        <v>0.1310377779887536</v>
+        <v>0.1924500242428656</v>
       </c>
       <c r="AL2">
-        <v>586.22</v>
+        <v>589.5</v>
       </c>
       <c r="AM2">
-        <v>586.22</v>
+        <v>589.5</v>
       </c>
       <c r="AN2">
-        <v>1.920362590819875</v>
+        <v>2.670340400082995</v>
       </c>
       <c r="AO2">
-        <v>19.10511412097847</v>
+        <v>13.09279050042409</v>
       </c>
       <c r="AP2">
-        <v>0.7247856478771394</v>
+        <v>1.22564778538562</v>
       </c>
       <c r="AQ2">
-        <v>19.10511412097847</v>
+        <v>13.09279050042409</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bâloise Holding AG (SWX:BALN)</t>
+          <t>Zurich Insurance Group AG (SWX:ZURN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0564</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0279</v>
+        <v>0.109</v>
+      </c>
+      <c r="F3">
+        <v>0.07580000000000001</v>
       </c>
       <c r="G3">
-        <v>0.08753668457274272</v>
+        <v>0.1727712508638563</v>
       </c>
       <c r="H3">
-        <v>0.08753668457274272</v>
+        <v>0.1727712508638563</v>
       </c>
       <c r="I3">
-        <v>0.229306468498464</v>
+        <v>0.1581537559422839</v>
       </c>
       <c r="J3">
-        <v>0.1892245723190309</v>
+        <v>0.1250024272822296</v>
       </c>
       <c r="K3">
-        <v>604.5</v>
+        <v>5213</v>
       </c>
       <c r="L3">
-        <v>0.05187327303619545</v>
+        <v>0.1091704885761555</v>
       </c>
       <c r="M3">
-        <v>363.9</v>
+        <v>3932</v>
       </c>
       <c r="N3">
-        <v>0.048714859437751</v>
+        <v>0.05543306020943885</v>
       </c>
       <c r="O3">
-        <v>0.601985111662531</v>
+        <v>0.7542681757145597</v>
       </c>
       <c r="P3">
-        <v>311.9</v>
+        <v>3450</v>
       </c>
       <c r="Q3">
-        <v>0.04175368139223561</v>
+        <v>0.0486378580169288</v>
       </c>
       <c r="R3">
-        <v>0.5159636062861869</v>
+        <v>0.6618070209092654</v>
       </c>
       <c r="S3">
-        <v>52</v>
+        <v>482</v>
       </c>
       <c r="T3">
-        <v>0.1428964001099203</v>
+        <v>0.1225839267548322</v>
       </c>
       <c r="U3">
-        <v>4699.4</v>
+        <v>6026</v>
       </c>
       <c r="V3">
-        <v>0.629103078982597</v>
+        <v>0.08495412533623563</v>
       </c>
       <c r="W3">
-        <v>0.09224078736552987</v>
+        <v>0.1430256804214223</v>
       </c>
       <c r="X3">
-        <v>0.05259737644141676</v>
+        <v>0.08194787761549327</v>
       </c>
       <c r="Y3">
-        <v>0.03964341092411312</v>
+        <v>0.06107780280592903</v>
       </c>
       <c r="Z3">
-        <v>2.369636829476595</v>
+        <v>1.126096594660881</v>
       </c>
       <c r="AA3">
-        <v>0.4483935156091331</v>
+        <v>0.1407648076868632</v>
       </c>
       <c r="AB3">
-        <v>0.04394240977822787</v>
+        <v>0.07375449392790163</v>
       </c>
       <c r="AC3">
-        <v>0.4044511058309052</v>
+        <v>0.06701031375896156</v>
       </c>
       <c r="AD3">
-        <v>2684.7</v>
+        <v>16620</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2684.7</v>
+        <v>16620</v>
       </c>
       <c r="AG3">
-        <v>-2014.7</v>
+        <v>10594</v>
       </c>
       <c r="AH3">
-        <v>0.2643800407692989</v>
+        <v>0.1898291765845368</v>
       </c>
       <c r="AI3">
-        <v>0.259013420034539</v>
+        <v>0.3639867720812072</v>
       </c>
       <c r="AJ3">
-        <v>-0.3693105787032793</v>
+        <v>0.1299456372414335</v>
       </c>
       <c r="AK3">
-        <v>-0.3555959546040207</v>
+        <v>0.2672890122366595</v>
       </c>
       <c r="AL3">
-        <v>66.59999999999999</v>
+        <v>450</v>
       </c>
       <c r="AM3">
-        <v>66.59999999999999</v>
+        <v>450</v>
       </c>
       <c r="AN3">
-        <v>0.9907738864080895</v>
+        <v>2.128313484441029</v>
       </c>
       <c r="AO3">
-        <v>40.12312312312312</v>
+        <v>16.78222222222222</v>
       </c>
       <c r="AP3">
-        <v>-0.7435140421448869</v>
+        <v>1.356639774619029</v>
       </c>
       <c r="AQ3">
-        <v>40.12312312312312</v>
+        <v>16.78222222222222</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zurich Insurance Group AG (SWX:ZURN)</t>
+          <t>Helvetia Holding AG (SWX:HELN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,124 +862,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0342</v>
+        <v>0.0319</v>
       </c>
       <c r="E4">
-        <v>0.283</v>
-      </c>
-      <c r="F4">
-        <v>0.0476</v>
+        <v>0.0266</v>
       </c>
       <c r="G4">
-        <v>0.08370710921731329</v>
+        <v>0.0924531560314308</v>
       </c>
       <c r="H4">
-        <v>0.08370710921731329</v>
+        <v>0.0924531560314308</v>
       </c>
       <c r="I4">
-        <v>0.1038349405696345</v>
+        <v>0.05896727398324842</v>
       </c>
       <c r="J4">
-        <v>0.0753126087453044</v>
+        <v>0.04466377411989675</v>
       </c>
       <c r="K4">
-        <v>4846</v>
+        <v>479.2</v>
       </c>
       <c r="L4">
-        <v>0.06792442251625926</v>
+        <v>0.0413781193333909</v>
       </c>
       <c r="M4">
-        <v>3389</v>
+        <v>316.7</v>
       </c>
       <c r="N4">
-        <v>0.05210567504447201</v>
+        <v>0.05139064680492</v>
       </c>
       <c r="O4">
-        <v>0.699339661576558</v>
+        <v>0.6608931552587646</v>
       </c>
       <c r="P4">
-        <v>3196</v>
+        <v>306.2</v>
       </c>
       <c r="Q4">
-        <v>0.04913831143172988</v>
+        <v>0.04968682049784182</v>
       </c>
       <c r="R4">
-        <v>0.6595130004127115</v>
+        <v>0.6389816360601002</v>
       </c>
       <c r="S4">
-        <v>193</v>
+        <v>10.5</v>
       </c>
       <c r="T4">
-        <v>0.05694895249336087</v>
+        <v>0.03315440479949479</v>
       </c>
       <c r="U4">
-        <v>7018</v>
+        <v>1489.9</v>
       </c>
       <c r="V4">
-        <v>0.1079013359286234</v>
+        <v>0.2417648395157888</v>
       </c>
       <c r="W4">
-        <v>0.1459902391998554</v>
+        <v>0.07615536202402899</v>
       </c>
       <c r="X4">
-        <v>0.05030108412008725</v>
+        <v>0.08709209810327748</v>
       </c>
       <c r="Y4">
-        <v>0.09568915507976816</v>
+        <v>-0.01093673607924849</v>
       </c>
       <c r="Z4">
-        <v>1.987741000780118</v>
+        <v>1.540579729424128</v>
       </c>
       <c r="AA4">
-        <v>0.1497019602787528</v>
+        <v>0.06880810504869091</v>
       </c>
       <c r="AB4">
-        <v>0.04391656175319858</v>
+        <v>0.07310317064235741</v>
       </c>
       <c r="AC4">
-        <v>0.1057853985255543</v>
+        <v>-0.004295065593666506</v>
       </c>
       <c r="AD4">
-        <v>17262</v>
+        <v>2512.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>17262</v>
+        <v>2512.1</v>
       </c>
       <c r="AG4">
-        <v>10244</v>
+        <v>1022.2</v>
       </c>
       <c r="AH4">
-        <v>0.2097374454606095</v>
+        <v>0.2895892653348242</v>
       </c>
       <c r="AI4">
-        <v>0.312338285052563</v>
+        <v>0.3138987117170026</v>
       </c>
       <c r="AJ4">
-        <v>0.1360697829179557</v>
+        <v>0.1422725754370337</v>
       </c>
       <c r="AK4">
-        <v>0.2123152811457232</v>
+        <v>0.1569476431751881</v>
       </c>
       <c r="AL4">
-        <v>448</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AM4">
-        <v>448</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AN4">
-        <v>2.253524804177546</v>
+        <v>2.975364207035414</v>
       </c>
       <c r="AO4">
-        <v>16.53571428571428</v>
+        <v>9.278532608695652</v>
       </c>
       <c r="AP4">
-        <v>1.33733681462141</v>
+        <v>1.210707094634608</v>
       </c>
       <c r="AQ4">
-        <v>16.53571428571428</v>
+        <v>9.278532608695652</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +987,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Helvetia Holding AG (SWX:HELN)</t>
+          <t>Vaudoise Assurances Holding SA (SWX:VAHN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,121 +996,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0602</v>
+        <v>0.011</v>
       </c>
       <c r="E5">
-        <v>0.09849999999999999</v>
+        <v>0.0207</v>
       </c>
       <c r="G5">
-        <v>0.04407383102139953</v>
+        <v>0.1488953612275343</v>
       </c>
       <c r="H5">
-        <v>0.04407383102139953</v>
+        <v>0.1488953612275343</v>
       </c>
       <c r="I5">
-        <v>0.07136445580925227</v>
+        <v>0.1216168217660013</v>
       </c>
       <c r="J5">
-        <v>0.05859804030453895</v>
+        <v>0.108758655588098</v>
       </c>
       <c r="K5">
-        <v>575.6</v>
+        <v>142.1</v>
       </c>
       <c r="L5">
-        <v>0.04341758880013276</v>
+        <v>0.1009448035803083</v>
       </c>
       <c r="M5">
-        <v>290.078</v>
+        <v>54.1</v>
       </c>
       <c r="N5">
-        <v>0.04677772044120493</v>
+        <v>0.0408486861975234</v>
       </c>
       <c r="O5">
-        <v>0.5039576094510075</v>
+        <v>0.3807178043631246</v>
       </c>
       <c r="P5">
-        <v>285.648</v>
+        <v>54.1</v>
       </c>
       <c r="Q5">
-        <v>0.0460633425788557</v>
+        <v>0.0408486861975234</v>
       </c>
       <c r="R5">
-        <v>0.4962612925642807</v>
+        <v>0.3807178043631246</v>
       </c>
       <c r="S5">
-        <v>4.430000000000007</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.01527175449361898</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1974.4</v>
+        <v>278.4</v>
       </c>
       <c r="V5">
-        <v>0.3183899890343805</v>
+        <v>0.2102083962549079</v>
       </c>
       <c r="W5">
-        <v>0.09410764501994638</v>
+        <v>0.05718079755341837</v>
       </c>
       <c r="X5">
-        <v>0.05311859142517474</v>
+        <v>0.07499386895787666</v>
       </c>
       <c r="Y5">
-        <v>0.04098905359477164</v>
+        <v>-0.01781307140445829</v>
       </c>
       <c r="Z5">
-        <v>2.042160879879232</v>
+        <v>0.6150921961024207</v>
       </c>
       <c r="AA5">
-        <v>0.1196666255475159</v>
+        <v>0.06689660031083003</v>
       </c>
       <c r="AB5">
-        <v>0.04394778672887743</v>
+        <v>0.07499386895787666</v>
       </c>
       <c r="AC5">
-        <v>0.0757188388186385</v>
+        <v>-0.008097268647046629</v>
       </c>
       <c r="AD5">
-        <v>2361</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2361</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>386.5999999999999</v>
+        <v>-278.4</v>
       </c>
       <c r="AH5">
-        <v>0.2757468874821891</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.2355629165502654</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.05868423449406478</v>
+        <v>-0.2661567877629063</v>
       </c>
       <c r="AK5">
-        <v>0.04803439192883056</v>
+        <v>-0.1345122481519061</v>
       </c>
       <c r="AL5">
-        <v>69</v>
+        <v>18.5</v>
       </c>
       <c r="AM5">
-        <v>69</v>
+        <v>18.5</v>
       </c>
       <c r="AN5">
-        <v>2.240463085974568</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>13.71159420289855</v>
+        <v>9.254054054054054</v>
       </c>
       <c r="AP5">
-        <v>0.366862782311634</v>
+        <v>-1.406060606060606</v>
       </c>
       <c r="AQ5">
-        <v>13.71159420289855</v>
+        <v>9.254054054054054</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vaudoise Assurances Holding SA (SWX:VAHN)</t>
+          <t>Bâloise Holding AG (SWX:BALN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1130,121 +1130,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0175</v>
+        <v>-0.059</v>
       </c>
       <c r="E6">
-        <v>0.0509</v>
+        <v>-0.0124</v>
       </c>
       <c r="G6">
-        <v>0.1296060991105464</v>
+        <v>0.2971539310266784</v>
       </c>
       <c r="H6">
-        <v>0.1296060991105464</v>
+        <v>0.2971539310266784</v>
       </c>
       <c r="I6">
-        <v>0.1160302280478834</v>
+        <v>-0.0973067021246499</v>
       </c>
       <c r="J6">
-        <v>0.1020739370222902</v>
+        <v>-0.08023795069284435</v>
       </c>
       <c r="K6">
-        <v>137.5</v>
+        <v>600.3</v>
       </c>
       <c r="L6">
-        <v>0.09195479168059921</v>
+        <v>0.08491526862251393</v>
       </c>
       <c r="M6">
-        <v>69.59999999999999</v>
+        <v>383.7</v>
       </c>
       <c r="N6">
-        <v>0.04891075193253689</v>
+        <v>0.05504073904062428</v>
       </c>
       <c r="O6">
-        <v>0.5061818181818182</v>
+        <v>0.6391804097951025</v>
       </c>
       <c r="P6">
-        <v>59.3</v>
+        <v>331.5</v>
       </c>
       <c r="Q6">
-        <v>0.04167252283907238</v>
+        <v>0.0475527886160202</v>
       </c>
       <c r="R6">
-        <v>0.4312727272727273</v>
+        <v>0.552223888055972</v>
       </c>
       <c r="S6">
-        <v>10.3</v>
+        <v>52.19999999999999</v>
       </c>
       <c r="T6">
-        <v>0.1479885057471264</v>
+        <v>0.1360437842064112</v>
       </c>
       <c r="U6">
-        <v>196.5</v>
+        <v>4042.5</v>
       </c>
       <c r="V6">
-        <v>0.1380885453267744</v>
+        <v>0.5798858159283911</v>
       </c>
       <c r="W6">
-        <v>0.0667637776159262</v>
+        <v>0.07835587114290189</v>
       </c>
       <c r="X6">
-        <v>0.04381734796752063</v>
+        <v>0.08668801082554167</v>
       </c>
       <c r="Y6">
-        <v>0.02294642964840557</v>
+        <v>-0.00833213968263978</v>
       </c>
       <c r="Z6">
-        <v>0.8006961178045515</v>
+        <v>1.251996812184539</v>
       </c>
       <c r="AA6">
-        <v>0.08173020510277408</v>
+        <v>-0.1004576584836614</v>
       </c>
       <c r="AB6">
-        <v>0.04381734796752063</v>
+        <v>0.07314847148250835</v>
       </c>
       <c r="AC6">
-        <v>0.03791285713525346</v>
+        <v>-0.1736061299661697</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2746.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2746.8</v>
       </c>
       <c r="AG6">
-        <v>-196.5</v>
+        <v>-1295.7</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.2826507511833711</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.3431312538256862</v>
       </c>
       <c r="AJ6">
-        <v>-0.1602119853240929</v>
+        <v>-0.2282970663377676</v>
       </c>
       <c r="AK6">
-        <v>-0.08586035130647558</v>
+        <v>-0.3269822843587543</v>
       </c>
       <c r="AL6">
-        <v>2.62</v>
+        <v>47.4</v>
       </c>
       <c r="AM6">
-        <v>2.62</v>
+        <v>47.4</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>-4.174468085106383</v>
       </c>
       <c r="AO6">
-        <v>66.22137404580153</v>
+        <v>-14.5126582278481</v>
       </c>
       <c r="AP6">
-        <v>-1.018662519440124</v>
+        <v>1.969148936170213</v>
       </c>
       <c r="AQ6">
-        <v>66.22137404580153</v>
+        <v>-14.5126582278481</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.024</v>
+        <v>-0.01805</v>
       </c>
       <c r="E2">
-        <v>0.02365</v>
+        <v>0.041905</v>
       </c>
       <c r="F2">
-        <v>0.07580000000000001</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1715256506870022</v>
+        <v>0.1067445308481346</v>
       </c>
       <c r="H2">
-        <v>0.1715256506870022</v>
+        <v>0.1067445308481346</v>
       </c>
       <c r="I2">
-        <v>0.1138224810534279</v>
+        <v>0.1116372658779388</v>
       </c>
       <c r="J2">
-        <v>0.0929554041707483</v>
+        <v>0.09396779279805229</v>
       </c>
       <c r="K2">
-        <v>6434.6</v>
+        <v>6219.1</v>
       </c>
       <c r="L2">
-        <v>0.09489286836132613</v>
+        <v>0.09408907985113014</v>
       </c>
       <c r="M2">
-        <v>4686.5</v>
+        <v>6526.6</v>
       </c>
       <c r="N2">
-        <v>0.05488309017620207</v>
+        <v>0.07071992024965326</v>
       </c>
       <c r="O2">
-        <v>0.7283281012028719</v>
+        <v>1.049444453377498</v>
       </c>
       <c r="P2">
-        <v>4141.8</v>
+        <v>4332.6</v>
       </c>
       <c r="Q2">
-        <v>0.0485041679060693</v>
+        <v>0.04694651525658808</v>
       </c>
       <c r="R2">
-        <v>0.6436763745998197</v>
+        <v>0.6966602884661768</v>
       </c>
       <c r="S2">
-        <v>544.7</v>
+        <v>2194</v>
       </c>
       <c r="T2">
-        <v>0.1162274618585298</v>
+        <v>0.3361627800079674</v>
       </c>
       <c r="U2">
-        <v>11836.8</v>
+        <v>12024.1</v>
       </c>
       <c r="V2">
-        <v>0.1386194733378147</v>
+        <v>0.1302888782940361</v>
       </c>
       <c r="W2">
-        <v>0.07725561658346544</v>
+        <v>0.139376001999748</v>
       </c>
       <c r="X2">
-        <v>0.08431794422051747</v>
+        <v>0.0744423486825682</v>
       </c>
       <c r="Y2">
-        <v>-0.007062327637052029</v>
+        <v>0.0649336533171798</v>
       </c>
       <c r="Z2">
-        <v>1.172024184014214</v>
+        <v>1.425681155419046</v>
       </c>
       <c r="AA2">
-        <v>0.06785235267976047</v>
+        <v>0.1079991803634563</v>
       </c>
       <c r="AB2">
-        <v>0.07345148270520499</v>
+        <v>0.06644315593789926</v>
       </c>
       <c r="AC2">
-        <v>-0.006196167120356567</v>
+        <v>0.04117504653994563</v>
       </c>
       <c r="AD2">
-        <v>21878.9</v>
+        <v>20888.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21878.9</v>
+        <v>20888.1</v>
       </c>
       <c r="AG2">
-        <v>10042.1</v>
+        <v>8863.999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.2039619836020491</v>
+        <v>0.1845628184749253</v>
       </c>
       <c r="AI2">
-        <v>0.3417664967641458</v>
+        <v>0.3657373280361673</v>
       </c>
       <c r="AJ2">
-        <v>0.1052270343393826</v>
+        <v>0.08763049667826635</v>
       </c>
       <c r="AK2">
-        <v>0.1924500242428656</v>
+        <v>0.1965924565629144</v>
       </c>
       <c r="AL2">
-        <v>589.5</v>
+        <v>682.8200000000001</v>
       </c>
       <c r="AM2">
-        <v>589.5</v>
+        <v>682.8200000000001</v>
       </c>
       <c r="AN2">
-        <v>2.670340400082995</v>
+        <v>2.703261291574997</v>
       </c>
       <c r="AO2">
-        <v>13.09279050042409</v>
+        <v>10.80665475527958</v>
       </c>
       <c r="AP2">
-        <v>1.22564778538562</v>
+        <v>1.147146369871878</v>
       </c>
       <c r="AQ2">
-        <v>13.09279050042409</v>
+        <v>10.80665475527958</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06619999999999999</v>
+        <v>-0.0572</v>
       </c>
       <c r="E3">
-        <v>0.109</v>
+        <v>0.0761</v>
       </c>
       <c r="F3">
-        <v>0.07580000000000001</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1727712508638563</v>
+        <v>0.1532364888731897</v>
       </c>
       <c r="H3">
-        <v>0.1727712508638563</v>
+        <v>0.1532364888731897</v>
       </c>
       <c r="I3">
-        <v>0.1581537559422839</v>
+        <v>0.1595284351819145</v>
       </c>
       <c r="J3">
-        <v>0.1250024272822296</v>
+        <v>0.1251487909111705</v>
       </c>
       <c r="K3">
-        <v>5213</v>
+        <v>4751</v>
       </c>
       <c r="L3">
-        <v>0.1091704885761555</v>
+        <v>0.1048878488166726</v>
       </c>
       <c r="M3">
-        <v>3932</v>
+        <v>5978</v>
       </c>
       <c r="N3">
-        <v>0.05543306020943885</v>
+        <v>0.07824044080596292</v>
       </c>
       <c r="O3">
-        <v>0.7542681757145597</v>
+        <v>1.258261418648706</v>
       </c>
       <c r="P3">
-        <v>3450</v>
+        <v>3877</v>
       </c>
       <c r="Q3">
-        <v>0.0486378580169288</v>
+        <v>0.05074242037549653</v>
       </c>
       <c r="R3">
-        <v>0.6618070209092654</v>
+        <v>0.8160387286886971</v>
       </c>
       <c r="S3">
-        <v>482</v>
+        <v>2101</v>
       </c>
       <c r="T3">
-        <v>0.1225839267548322</v>
+        <v>0.3514553362328538</v>
       </c>
       <c r="U3">
-        <v>6026</v>
+        <v>6437</v>
       </c>
       <c r="V3">
-        <v>0.08495412533623563</v>
+        <v>0.08424786173770213</v>
       </c>
       <c r="W3">
-        <v>0.1430256804214223</v>
+        <v>0.1710223182145428</v>
       </c>
       <c r="X3">
-        <v>0.08194787761549327</v>
+        <v>0.07239997577276677</v>
       </c>
       <c r="Y3">
-        <v>0.06107780280592903</v>
+        <v>0.09862234244177606</v>
       </c>
       <c r="Z3">
-        <v>1.126096594660881</v>
+        <v>1.326655537006121</v>
       </c>
       <c r="AA3">
-        <v>0.1407648076868632</v>
+        <v>0.1660293364119257</v>
       </c>
       <c r="AB3">
-        <v>0.07375449392790163</v>
+        <v>0.06667186460529394</v>
       </c>
       <c r="AC3">
-        <v>0.06701031375896156</v>
+        <v>0.09935747180663172</v>
       </c>
       <c r="AD3">
-        <v>16620</v>
+        <v>15517</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16620</v>
+        <v>15517</v>
       </c>
       <c r="AG3">
-        <v>10594</v>
+        <v>9080</v>
       </c>
       <c r="AH3">
-        <v>0.1898291765845368</v>
+        <v>0.1688052435475536</v>
       </c>
       <c r="AI3">
-        <v>0.3639867720812072</v>
+        <v>0.3798345246254773</v>
       </c>
       <c r="AJ3">
-        <v>0.1299456372414335</v>
+        <v>0.1062168437922221</v>
       </c>
       <c r="AK3">
-        <v>0.2672890122366595</v>
+        <v>0.2638384425395903</v>
       </c>
       <c r="AL3">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AM3">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AN3">
-        <v>2.128313484441029</v>
+        <v>2.113744721427599</v>
       </c>
       <c r="AO3">
-        <v>16.78222222222222</v>
+        <v>16.42272727272727</v>
       </c>
       <c r="AP3">
-        <v>1.356639774619029</v>
+        <v>1.236888707260591</v>
       </c>
       <c r="AQ3">
-        <v>16.78222222222222</v>
+        <v>16.42272727272727</v>
       </c>
     </row>
     <row r="4">
@@ -862,121 +862,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0319</v>
+        <v>0.0277</v>
       </c>
       <c r="E4">
-        <v>0.0266</v>
+        <v>0.0883</v>
       </c>
       <c r="G4">
-        <v>0.0924531560314308</v>
+        <v>0.07051224908223053</v>
       </c>
       <c r="H4">
-        <v>0.0924531560314308</v>
+        <v>0.07051224908223053</v>
       </c>
       <c r="I4">
-        <v>0.05896727398324842</v>
+        <v>0.07851892671620865</v>
       </c>
       <c r="J4">
-        <v>0.04466377411989675</v>
+        <v>0.06843417455662228</v>
       </c>
       <c r="K4">
-        <v>479.2</v>
+        <v>716</v>
       </c>
       <c r="L4">
-        <v>0.0413781193333909</v>
+        <v>0.05802410107214924</v>
       </c>
       <c r="M4">
-        <v>316.7</v>
+        <v>51.6</v>
       </c>
       <c r="N4">
-        <v>0.05139064680492</v>
+        <v>0.00708567348227895</v>
       </c>
       <c r="O4">
-        <v>0.6608931552587646</v>
+        <v>0.07206703910614526</v>
       </c>
       <c r="P4">
-        <v>306.2</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>0.04968682049784182</v>
+        <v>0.002609065817118218</v>
       </c>
       <c r="R4">
-        <v>0.6389816360601002</v>
+        <v>0.02653631284916201</v>
       </c>
       <c r="S4">
-        <v>10.5</v>
+        <v>32.6</v>
       </c>
       <c r="T4">
-        <v>0.03315440479949479</v>
+        <v>0.6317829457364341</v>
       </c>
       <c r="U4">
-        <v>1489.9</v>
+        <v>1382</v>
       </c>
       <c r="V4">
-        <v>0.2417648395157888</v>
+        <v>0.1897752083819672</v>
       </c>
       <c r="W4">
-        <v>0.07615536202402899</v>
+        <v>0.1638706428947428</v>
       </c>
       <c r="X4">
-        <v>0.08709209810327748</v>
+        <v>0.07648472159236963</v>
       </c>
       <c r="Y4">
-        <v>-0.01093673607924849</v>
+        <v>0.08738592130237322</v>
       </c>
       <c r="Z4">
-        <v>1.540579729424128</v>
+        <v>1.989279553771501</v>
       </c>
       <c r="AA4">
-        <v>0.06880810504869091</v>
+        <v>0.1361347042247186</v>
       </c>
       <c r="AB4">
-        <v>0.07310317064235741</v>
+        <v>0.06621444727050457</v>
       </c>
       <c r="AC4">
-        <v>-0.004295065593666506</v>
+        <v>0.06992025695421403</v>
       </c>
       <c r="AD4">
-        <v>2512.1</v>
+        <v>2695.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2512.1</v>
+        <v>2695.4</v>
       </c>
       <c r="AG4">
-        <v>1022.2</v>
+        <v>1313.4</v>
       </c>
       <c r="AH4">
-        <v>0.2895892653348242</v>
+        <v>0.2701424175912284</v>
       </c>
       <c r="AI4">
-        <v>0.3138987117170026</v>
+        <v>0.3675361686461131</v>
       </c>
       <c r="AJ4">
-        <v>0.1422725754370337</v>
+        <v>0.1527973288970066</v>
       </c>
       <c r="AK4">
-        <v>0.1569476431751881</v>
+        <v>0.2206764453853521</v>
       </c>
       <c r="AL4">
-        <v>73.59999999999999</v>
+        <v>165.3</v>
       </c>
       <c r="AM4">
-        <v>73.59999999999999</v>
+        <v>165.3</v>
       </c>
       <c r="AN4">
-        <v>2.975364207035414</v>
+        <v>2.341789748045178</v>
       </c>
       <c r="AO4">
-        <v>9.278532608695652</v>
+        <v>5.861464004839685</v>
       </c>
       <c r="AP4">
-        <v>1.210707094634608</v>
+        <v>1.141094700260643</v>
       </c>
       <c r="AQ4">
-        <v>9.278532608695652</v>
+        <v>5.861464004839685</v>
       </c>
     </row>
     <row r="5">
@@ -996,79 +996,79 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.011</v>
+        <v>0.0211</v>
       </c>
       <c r="E5">
-        <v>0.0207</v>
+        <v>-0.00398</v>
       </c>
       <c r="G5">
-        <v>0.1488953612275343</v>
+        <v>0.1183710961420698</v>
       </c>
       <c r="H5">
-        <v>0.1488953612275343</v>
+        <v>0.1183710961420698</v>
       </c>
       <c r="I5">
-        <v>0.1216168217660013</v>
+        <v>0.1140232700551133</v>
       </c>
       <c r="J5">
-        <v>0.108758655588098</v>
+        <v>0.1011964960406245</v>
       </c>
       <c r="K5">
-        <v>142.1</v>
+        <v>149.8</v>
       </c>
       <c r="L5">
-        <v>0.1009448035803083</v>
+        <v>0.09173300673606859</v>
       </c>
       <c r="M5">
-        <v>54.1</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N5">
-        <v>0.0408486861975234</v>
+        <v>0.04931253305129561</v>
       </c>
       <c r="O5">
-        <v>0.3807178043631246</v>
+        <v>0.4979973297730306</v>
       </c>
       <c r="P5">
-        <v>54.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q5">
-        <v>0.0408486861975234</v>
+        <v>0.04091750396615548</v>
       </c>
       <c r="R5">
-        <v>0.3807178043631246</v>
+        <v>0.4132176234979973</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.1702412868632707</v>
       </c>
       <c r="U5">
-        <v>278.4</v>
+        <v>362.5</v>
       </c>
       <c r="V5">
-        <v>0.2102083962549079</v>
+        <v>0.2396218931782126</v>
       </c>
       <c r="W5">
-        <v>0.05718079755341837</v>
+        <v>0.0638098483557676</v>
       </c>
       <c r="X5">
-        <v>0.07499386895787666</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="Y5">
-        <v>-0.01781307140445829</v>
+        <v>-0.003623972020749183</v>
       </c>
       <c r="Z5">
-        <v>0.6150921961024207</v>
+        <v>0.7891938913589794</v>
       </c>
       <c r="AA5">
-        <v>0.06689660031083003</v>
+        <v>0.07986365650219401</v>
       </c>
       <c r="AB5">
-        <v>0.07499386895787666</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AC5">
-        <v>-0.008097268647046629</v>
+        <v>0.01242983612567723</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-278.4</v>
+        <v>-362.5</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1089,28 +1089,28 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.2661567877629063</v>
+        <v>-0.3151351821264018</v>
       </c>
       <c r="AK5">
-        <v>-0.1345122481519061</v>
+        <v>-0.1630899356638323</v>
       </c>
       <c r="AL5">
-        <v>18.5</v>
+        <v>2.32</v>
       </c>
       <c r="AM5">
-        <v>18.5</v>
+        <v>2.32</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>9.254054054054054</v>
+        <v>80.25862068965517</v>
       </c>
       <c r="AP5">
-        <v>-1.406060606060606</v>
+        <v>-1.775220372184133</v>
       </c>
       <c r="AQ5">
-        <v>9.254054054054054</v>
+        <v>80.25862068965517</v>
       </c>
     </row>
     <row r="6">
@@ -1130,121 +1130,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.059</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.0124</v>
+        <v>0.00771</v>
       </c>
       <c r="G6">
-        <v>0.2971539310266784</v>
+        <v>-0.1389307835356479</v>
       </c>
       <c r="H6">
-        <v>0.2971539310266784</v>
+        <v>-0.1389307835356479</v>
       </c>
       <c r="I6">
-        <v>-0.0973067021246499</v>
+        <v>-0.1467353901571171</v>
       </c>
       <c r="J6">
-        <v>-0.08023795069284435</v>
+        <v>-0.1208123402617555</v>
       </c>
       <c r="K6">
-        <v>600.3</v>
+        <v>602.3</v>
       </c>
       <c r="L6">
-        <v>0.08491526862251393</v>
+        <v>0.08819351910151844</v>
       </c>
       <c r="M6">
-        <v>383.7</v>
+        <v>422.4</v>
       </c>
       <c r="N6">
-        <v>0.05504073904062428</v>
+        <v>0.05959872449699467</v>
       </c>
       <c r="O6">
-        <v>0.6391804097951025</v>
+        <v>0.7013116387182468</v>
       </c>
       <c r="P6">
-        <v>331.5</v>
+        <v>374.7</v>
       </c>
       <c r="Q6">
-        <v>0.0475527886160202</v>
+        <v>0.05286847080734825</v>
       </c>
       <c r="R6">
-        <v>0.552223888055972</v>
+        <v>0.6221152249709447</v>
       </c>
       <c r="S6">
-        <v>52.19999999999999</v>
+        <v>47.69999999999999</v>
       </c>
       <c r="T6">
-        <v>0.1360437842064112</v>
+        <v>0.1129261363636363</v>
       </c>
       <c r="U6">
-        <v>4042.5</v>
+        <v>3842.6</v>
       </c>
       <c r="V6">
-        <v>0.5798858159283911</v>
+        <v>0.5421734345458137</v>
       </c>
       <c r="W6">
-        <v>0.07835587114290189</v>
+        <v>0.1148813611047532</v>
       </c>
       <c r="X6">
-        <v>0.08668801082554167</v>
+        <v>0.07666564703466432</v>
       </c>
       <c r="Y6">
-        <v>-0.00833213968263978</v>
+        <v>0.03821571407008885</v>
       </c>
       <c r="Z6">
-        <v>1.251996812184539</v>
+        <v>1.730206987408477</v>
       </c>
       <c r="AA6">
-        <v>-0.1004576584836614</v>
+        <v>-0.2090303552860598</v>
       </c>
       <c r="AB6">
-        <v>0.07314847148250835</v>
+        <v>0.06619675255286536</v>
       </c>
       <c r="AC6">
-        <v>-0.1736061299661697</v>
+        <v>-0.2752271078389252</v>
       </c>
       <c r="AD6">
-        <v>2746.8</v>
+        <v>2675.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2746.8</v>
+        <v>2675.7</v>
       </c>
       <c r="AG6">
-        <v>-1295.7</v>
+        <v>-1166.9</v>
       </c>
       <c r="AH6">
-        <v>0.2826507511833711</v>
+        <v>0.2740625416107589</v>
       </c>
       <c r="AI6">
-        <v>0.3431312538256862</v>
+        <v>0.4219415271075788</v>
       </c>
       <c r="AJ6">
-        <v>-0.2282970663377676</v>
+        <v>-0.197094839962841</v>
       </c>
       <c r="AK6">
-        <v>-0.3269822843587543</v>
+        <v>-0.4669841523931488</v>
       </c>
       <c r="AL6">
-        <v>47.4</v>
+        <v>75.2</v>
       </c>
       <c r="AM6">
-        <v>47.4</v>
+        <v>75.2</v>
       </c>
       <c r="AN6">
-        <v>-4.174468085106383</v>
+        <v>-2.760730499380932</v>
       </c>
       <c r="AO6">
-        <v>-14.5126582278481</v>
+        <v>-13.32579787234043</v>
       </c>
       <c r="AP6">
-        <v>1.969148936170213</v>
+        <v>1.203982666116385</v>
       </c>
       <c r="AQ6">
-        <v>-14.5126582278481</v>
+        <v>-13.32579787234043</v>
       </c>
     </row>
   </sheetData>
